--- a/artfynd/A 66246-2021 artfynd.xlsx
+++ b/artfynd/A 66246-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 66246-2021 artfynd.xlsx
+++ b/artfynd/A 66246-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>95753586</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557108.1289121966</v>
+        <v>557109</v>
       </c>
       <c r="R2" t="n">
-        <v>6550387.345506908</v>
+        <v>6550388</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2021-08-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-08-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -800,16 +785,11 @@
         <v>95753891</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -840,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557156.8674386578</v>
+        <v>557157</v>
       </c>
       <c r="R3" t="n">
-        <v>6550398.865851193</v>
+        <v>6550399</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -873,19 +853,9 @@
           <t>2021-08-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,6 +880,318 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>95753377</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fagermon, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>556965</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6550395</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-08-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-08-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>95753443</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fagermon, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>557027</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6550400</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-08-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-08-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>95753384</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fagermon, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>556965</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6550395</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-08-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-08-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Lst D inventering sandbarrskogar</t>
         </is>

--- a/artfynd/A 66246-2021 artfynd.xlsx
+++ b/artfynd/A 66246-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95753586</t>
         </is>
       </c>
     </row>
@@ -884,6 +894,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95753891</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95753377</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95753443</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,8 +1221,20 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95753384</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>